--- a/artfynd/A 61224-2025 artfynd.xlsx
+++ b/artfynd/A 61224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90015126</v>
+        <v>90015121</v>
       </c>
       <c r="B2" t="n">
-        <v>97055</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,8 +703,16 @@
           <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>737356.3535779666</v>
+        <v>737408</v>
       </c>
       <c r="R2" t="n">
-        <v>7109051.411803045</v>
+        <v>7109034</v>
       </c>
       <c r="S2" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +755,14 @@
           <t>2020-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikligt i vägdiket</t>
+          <t>känd lokal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +787,573 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90015123</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99884</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>269</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Älvstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex rhynchophysa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dansarhällevägen, N om Kvarnlund, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>737344</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7109086</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>flera m2</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>90015126</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99884</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>269</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Älvstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex rhynchophysa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dansarhällevägen, N om Kvarnlund, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>737356</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7109051</v>
+      </c>
+      <c r="S4" t="n">
+        <v>27</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt i vägdiket</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86276795</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43249</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dansarhällavägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>737402</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7109025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Höll till nära skogskanten på planen direkt söder om vägen mot Dansarhällan.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Vidmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Vidmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110630887</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stormyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>737366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7109027</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Suzanne Bruks</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Suzanne Bruks</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79083117</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dansarhällan, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>737369</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7108954</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Belsing</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Belsing</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
